--- a/src/test/resources/LoginTestData.xlsx
+++ b/src/test/resources/LoginTestData.xlsx
@@ -3,12 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77CE6E0-0A68-4E5F-BE65-AEDE5B1DE0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{D5847AE9-FCCD-42B5-8E23-53D30091D975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +12,7 @@
     <sheet name="Legend" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="D1:I12"/>
 </workbook>
 </file>
 
@@ -596,8 +592,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -613,6 +607,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -969,10 +965,10 @@
       <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>133</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -996,10 +992,10 @@
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>133</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1023,10 +1019,10 @@
       <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>134</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -1050,10 +1046,10 @@
       <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="13" t="s">
         <v>135</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1077,10 +1073,10 @@
       <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="13" t="s">
         <v>133</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -1107,7 +1103,7 @@
       <c r="D7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="13" t="s">
         <v>133</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -1131,7 +1127,7 @@
       <c r="C8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="14" t="s">
         <v>133</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -1190,7 +1186,7 @@
         <v>44</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="14" t="s">
         <v>133</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -1214,7 +1210,7 @@
       <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="14" t="s">
         <v>133</v>
       </c>
       <c r="E11" s="3"/>
@@ -1316,10 +1312,10 @@
       <c r="C15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="14" t="s">
         <v>138</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -1345,10 +1341,10 @@
       <c r="C16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="14" t="s">
         <v>136</v>
       </c>
       <c r="F16" s="3" t="s">
@@ -1374,7 +1370,7 @@
       <c r="C17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="14" t="s">
         <v>133</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -1401,7 +1397,7 @@
       <c r="C18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="E18" s="4" t="s">
@@ -1428,7 +1424,7 @@
       <c r="C19" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="15" t="s">
         <v>133</v>
       </c>
       <c r="E19" s="4" t="s">
@@ -1455,7 +1451,7 @@
       <c r="C20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="15" t="s">
         <v>133</v>
       </c>
       <c r="E20" s="4" t="s">
@@ -1511,7 +1507,7 @@
       <c r="C22" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="15" t="s">
         <v>133</v>
       </c>
       <c r="E22" s="4" t="s">
@@ -1538,10 +1534,10 @@
       <c r="C23" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="15" t="s">
         <v>133</v>
       </c>
       <c r="F23" s="4" t="s">
@@ -1592,7 +1588,7 @@
       <c r="C25" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="15" t="s">
         <v>133</v>
       </c>
       <c r="E25" s="4" t="s">
@@ -1702,7 +1698,7 @@
       <c r="C29" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="16" t="s">
         <v>133</v>
       </c>
       <c r="E29" s="5" t="s">
@@ -1729,10 +1725,10 @@
       <c r="C30" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="16" t="s">
         <v>133</v>
       </c>
       <c r="F30" s="5" t="s">
@@ -1747,7 +1743,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D31" s="19"/>
+      <c r="D31" s="17"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1858,19 +1854,19 @@
       <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="14"/>
+      <c r="C8" s="19"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
